--- a/dist/成果/防治对象/测量表/360481106200106_永丰村老屋陈家/沟道纵断面成果表_AFAE900121D00000ZACS004.xlsx
+++ b/dist/成果/防治对象/测量表/360481106200106_永丰村老屋陈家/沟道纵断面成果表_AFAE900121D00000ZACS004.xlsx
@@ -822,7 +822,7 @@
         <v>37.77500000000001</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>37.79737182863384</v>
+        <v>38.11547022127116</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.552437</v>
@@ -850,7 +850,7 @@
         <v>37.971</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>38.25585779485043</v>
+        <v>38.15415397424006</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.552587</v>
@@ -878,7 +878,7 @@
         <v>37.836</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>38.195</v>
+        <v>37.85983294019961</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.552679</v>
@@ -906,7 +906,7 @@
         <v>37.68</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>37.80712014513374</v>
+        <v>37.85105084562021</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.552779</v>
@@ -934,7 +934,7 @@
         <v>37.702</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>37.81502299738312</v>
+        <v>38.0849214981929</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.552815</v>
@@ -962,7 +962,7 @@
         <v>37.722</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>38.20103219669989</v>
+        <v>37.93984600569454</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.552892</v>
@@ -990,7 +990,7 @@
         <v>37.677</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>38.195</v>
+        <v>37.73587710185767</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.552985</v>
@@ -1018,7 +1018,7 @@
         <v>37.562</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>37.94214855095166</v>
+        <v>37.79343770021103</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.553084</v>
@@ -1046,7 +1046,7 @@
         <v>37.463</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>37.78333693934266</v>
+        <v>37.55171348047296</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.553239</v>
@@ -1074,7 +1074,7 @@
         <v>23.424</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>37.59592765155913</v>
+        <v>37.08303409765485</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.553326</v>
@@ -1102,7 +1102,7 @@
         <v>37.181</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>37.52488276681506</v>
+        <v>37.54658331159135</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.553398</v>
@@ -1130,7 +1130,7 @@
         <v>37.50700000000001</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>37.78595547742502</v>
+        <v>37.89503904277782</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.553445</v>
@@ -1158,7 +1158,7 @@
         <v>37.433</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>37.62301921442811</v>
+        <v>37.652644759672</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.553483</v>
@@ -1186,7 +1186,7 @@
         <v>37.14100000000001</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>37.21793462887193</v>
+        <v>37.18939431692331</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.55345</v>
@@ -1214,7 +1214,7 @@
         <v>37.062</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>37.2295970894906</v>
+        <v>37.35868463671638</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.553413</v>
@@ -1242,7 +1242,7 @@
         <v>37.193</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>37.54379265096229</v>
+        <v>37.47714564707202</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.553314</v>
@@ -1270,7 +1270,7 @@
         <v>37.223</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>37.23355760054425</v>
+        <v>37.5990869765525</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>115.553264</v>
@@ -1298,7 +1298,7 @@
         <v>36.926</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>37.34020537842607</v>
+        <v>37.50404032154638</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.553153</v>
@@ -1326,7 +1326,7 @@
         <v>36.839</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>37.10060573956875</v>
+        <v>37.44365986336979</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.553079</v>
@@ -1354,7 +1354,7 @@
         <v>36.65000000000001</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>36.86885191365486</v>
+        <v>37.15089974903119</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.55293</v>
@@ -1382,7 +1382,7 @@
         <v>36.75</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>36.83805127311354</v>
+        <v>37.07728402820998</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>115.552796</v>
@@ -1410,7 +1410,7 @@
         <v>36.717</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>36.82798230438367</v>
+        <v>36.85992559458349</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>115.552629</v>
@@ -1438,7 +1438,7 @@
         <v>36.594</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>36.74823572494175</v>
+        <v>37.00465786939371</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>115.552577</v>
@@ -1466,7 +1466,7 @@
         <v>36.375</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>36.38466707500137</v>
+        <v>36.52544356046186</v>
       </c>
       <c r="G35" s="23" t="n">
         <v>115.55243</v>
@@ -1494,7 +1494,7 @@
         <v>36.443</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>36.76972127652003</v>
+        <v>36.72654385490414</v>
       </c>
       <c r="G36" s="23" t="n">
         <v>115.552291</v>
@@ -1522,7 +1522,7 @@
         <v>36.739</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>36.79492274572974</v>
+        <v>36.97628711058142</v>
       </c>
       <c r="G37" s="23" t="n">
         <v>115.552201</v>
@@ -1550,7 +1550,7 @@
         <v>36.596</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>36.73704898312964</v>
+        <v>36.69431310733547</v>
       </c>
       <c r="G38" s="23" t="n">
         <v>115.552152</v>
@@ -1578,7 +1578,7 @@
         <v>36.484</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>36.73813105021414</v>
+        <v>36.86556030169095</v>
       </c>
       <c r="G39" s="23" t="n">
         <v>115.55203</v>
@@ -1606,7 +1606,7 @@
         <v>36.39100000000001</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>36.65423021087696</v>
+        <v>36.80902401371847</v>
       </c>
       <c r="G40" s="23" t="n">
         <v>115.551955</v>
@@ -1634,7 +1634,7 @@
         <v>36.367</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>36.49177278442244</v>
+        <v>36.43455906184095</v>
       </c>
       <c r="G41" s="23" t="n">
         <v>115.551965</v>
@@ -1662,7 +1662,7 @@
         <v>36.366</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>36.43590936985191</v>
+        <v>36.37175963215373</v>
       </c>
       <c r="G42" s="23" t="n">
         <v>115.55189</v>
@@ -1690,7 +1690,7 @@
         <v>36.252</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>36.32079512094032</v>
+        <v>36.34799860521571</v>
       </c>
       <c r="G43" s="23" t="n">
         <v>115.551844</v>
@@ -1718,7 +1718,7 @@
         <v>36.186</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>36.30157609029915</v>
+        <v>36.58154484622766</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>115.551859</v>
@@ -1746,7 +1746,7 @@
         <v>36.247</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>36.43554027837539</v>
+        <v>36.573</v>
       </c>
       <c r="G45" s="23" t="n">
         <v>115.55191</v>
@@ -1774,7 +1774,7 @@
         <v>36.089</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>36.43451777261245</v>
+        <v>36.33324900875949</v>
       </c>
       <c r="G46" s="23" t="n">
         <v>115.551969</v>
@@ -1802,7 +1802,7 @@
         <v>36.035</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>36.058355955737</v>
+        <v>36.18667822760398</v>
       </c>
       <c r="G47" s="23" t="n">
         <v>115.552076</v>
@@ -1830,7 +1830,7 @@
         <v>35.984</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>36.00680671077331</v>
+        <v>36.44631774811785</v>
       </c>
       <c r="G48" s="23" t="n">
         <v>115.55213</v>
@@ -1858,7 +1858,7 @@
         <v>35.806</v>
       </c>
       <c r="F49" s="22" t="n">
-        <v>35.80894855739565</v>
+        <v>36.32</v>
       </c>
       <c r="G49" s="23" t="n">
         <v>115.552327</v>
@@ -1886,7 +1886,7 @@
         <v>35.78</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>36.0411269408946</v>
+        <v>36.12743484046067</v>
       </c>
       <c r="G50" s="23" t="n">
         <v>115.55245</v>
@@ -1914,7 +1914,7 @@
         <v>35.633</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>35.82037881739273</v>
+        <v>36.0057445716435</v>
       </c>
       <c r="G51" s="23" t="n">
         <v>115.55248</v>
@@ -1942,7 +1942,7 @@
         <v>35.823</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>36.2591780089376</v>
+        <v>35.9818307323382</v>
       </c>
       <c r="G52" s="23" t="n">
         <v>115.552702</v>
@@ -1970,7 +1970,7 @@
         <v>35.681</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>36.00190176887386</v>
+        <v>35.72331975091679</v>
       </c>
       <c r="G53" s="23" t="n">
         <v>115.552877</v>
@@ -1998,7 +1998,7 @@
         <v>35.624</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>35.92496231975727</v>
+        <v>35.76645909479926</v>
       </c>
       <c r="G54" s="23" t="n">
         <v>115.552995</v>
@@ -2026,7 +2026,7 @@
         <v>35.518</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>35.90015531775501</v>
+        <v>35.97229190274512</v>
       </c>
       <c r="G55" s="23" t="n">
         <v>115.553141</v>
@@ -2054,7 +2054,7 @@
         <v>35.351</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>35.73089234200043</v>
+        <v>35.55709081352344</v>
       </c>
       <c r="G56" s="23" t="n">
         <v>115.553786</v>
@@ -2078,16 +2078,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
